--- a/banco_de_dados/entrega_orientadora/Dicionario_Variaveis_Projeto.xlsx
+++ b/banco_de_dados/entrega_orientadora/Dicionario_Variaveis_Projeto.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="289">
   <si>
     <t>variavel</t>
   </si>
@@ -265,6 +265,33 @@
     <t>V01063</t>
   </si>
   <si>
+    <t>CD_UF</t>
+  </si>
+  <si>
+    <t>CD_MUN</t>
+  </si>
+  <si>
+    <t>Dados_sig</t>
+  </si>
+  <si>
+    <t>Moradia_Predominante</t>
+  </si>
+  <si>
+    <t>Moradia_Predominante_Agrupada</t>
+  </si>
+  <si>
+    <t>urbano</t>
+  </si>
+  <si>
+    <t>is_fcu</t>
+  </si>
+  <si>
+    <t>renda_media_sem_extremo</t>
+  </si>
+  <si>
+    <t>renda_media_mediana_mun</t>
+  </si>
+  <si>
     <t>Código da Favela ou Comunidade Urbana à qual o setor pertence</t>
   </si>
   <si>
@@ -478,6 +505,33 @@
     <t>Pessoa responsável pelo domicílio, Sexo feminino</t>
   </si>
   <si>
+    <t>Código IBGE da Unidade da Federação (2 primeiros dígitos do CD_SETOR)</t>
+  </si>
+  <si>
+    <t>Código IBGE do município (7 primeiros dígitos do CD_SETOR)</t>
+  </si>
+  <si>
+    <t>Elegibilidade do setor: OK / SIGILOSO / ZERADO / COLETIVO (regra do Cálculo IVS2012.docx)</t>
+  </si>
+  <si>
+    <t>Tipo de moradia com maior contagem no setor (classificação derivada)</t>
+  </si>
+  <si>
+    <t>Moradia predominante agrupada em Convencional / Não convencional / Indefinido</t>
+  </si>
+  <si>
+    <t>1 se SITUACAO = Urbana (recorte de análise do IVS); 0 caso contrário</t>
+  </si>
+  <si>
+    <t>1 se o setor é de Favela e Comunidade Urbana (CD_TIPO = 1)</t>
+  </si>
+  <si>
+    <t>Igual a renda_media, exceto nos setores excluídos nominalmente, onde fica vazia. Hoje é um só: 310620005650366 — Belo Horizonte, bairro Senhor dos Passos: R$ 170.418,06, maior valor da base e 55,7× a mediana do município. Setor de favela (CD_TIPO=1) com 186 domicílios, 518 pessoas e 31 analfabetos — classificado SUSPEITO por três testes de incoerência. Excluído a pedido da orientadora em 01/09/2026. A coluna renda_media continua ao lado, sem alteração, para a exclusão ser auditável.</t>
+  </si>
+  <si>
+    <t>Igual a renda_media, exceto nos setores de SETORES_RENDA_EXCLUIDA, onde entra a mediana do próprio município (sem eles), no recorte urbano e Dados_sig=OK — alternativa a deixar vazio, já que a mediana do setor (V06006) não existe no arquivo.</t>
+  </si>
+  <si>
     <t>Básico</t>
   </si>
   <si>
@@ -502,12 +556,18 @@
     <t>Parentesco</t>
   </si>
   <si>
+    <t>(derivado)</t>
+  </si>
+  <si>
     <t>Domicílio 1</t>
   </si>
   <si>
     <t>Domicílio 2</t>
   </si>
   <si>
+    <t>Colunas derivadas pela pipeline</t>
+  </si>
+  <si>
     <t>Agregados_por_setores_basico_BR_20250417.csv</t>
   </si>
   <si>
@@ -629,6 +689,9 @@
   </si>
   <si>
     <t>Dicionário oficial IBGE</t>
+  </si>
+  <si>
+    <t>Documentação do projeto (gerar_entrega_orientadora.py)</t>
   </si>
   <si>
     <t>indicador</t>
@@ -1158,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1197,25 +1260,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H2" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1223,25 +1286,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H3" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1249,25 +1312,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H4" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1275,25 +1338,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H5" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1301,25 +1364,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H6" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1327,25 +1390,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E7" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H7" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1353,25 +1416,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E8" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H8" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1379,25 +1442,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E9" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H9" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1405,25 +1468,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E10" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H10" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1431,25 +1494,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E11" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H11" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1457,25 +1520,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E12" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="H12" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1483,25 +1546,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E13" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="H13" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1509,25 +1572,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E14" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H14" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1535,25 +1598,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E15" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H15" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1561,25 +1624,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E16" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="H16" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1587,25 +1650,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D17" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E17" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F17" t="s">
         <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="H17" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1613,25 +1676,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="H18" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1639,25 +1702,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D19" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E19" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F19" t="s">
         <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="H19" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1665,25 +1728,25 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E20" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="H20" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1691,25 +1754,25 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E21" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="H21" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1717,25 +1780,25 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E22" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F22" t="s">
         <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H22" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1743,25 +1806,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E23" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F23" t="s">
         <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H23" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1769,25 +1832,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E24" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H24" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1795,25 +1858,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D25" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E25" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F25" t="s">
         <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H25" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1821,25 +1884,25 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E26" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F26" t="s">
         <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H26" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1847,25 +1910,25 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E27" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F27" t="s">
         <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H27" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1873,25 +1936,25 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D28" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E28" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F28" t="s">
         <v>57</v>
       </c>
       <c r="G28" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H28" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1899,25 +1962,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D29" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E29" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F29" t="s">
         <v>57</v>
       </c>
       <c r="G29" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H29" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1925,25 +1988,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D30" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E30" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F30" t="s">
         <v>57</v>
       </c>
       <c r="G30" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H30" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1951,25 +2014,25 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E31" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F31" t="s">
         <v>57</v>
       </c>
       <c r="G31" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H31" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1977,25 +2040,25 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E32" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F32" t="s">
         <v>57</v>
       </c>
       <c r="G32" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H32" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2003,25 +2066,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D33" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E33" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F33" t="s">
         <v>57</v>
       </c>
       <c r="G33" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H33" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2029,25 +2092,25 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E34" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F34" t="s">
         <v>57</v>
       </c>
       <c r="G34" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H34" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2055,25 +2118,25 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E35" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F35" t="s">
         <v>57</v>
       </c>
       <c r="G35" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="H35" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2081,25 +2144,25 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E36" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F36" t="s">
         <v>57</v>
       </c>
       <c r="G36" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="H36" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2107,25 +2170,25 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E37" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F37" t="s">
         <v>57</v>
       </c>
       <c r="G37" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="H37" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2133,25 +2196,25 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D38" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E38" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F38" t="s">
         <v>57</v>
       </c>
       <c r="G38" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="H38" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2159,25 +2222,25 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C39" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D39" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E39" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F39" t="s">
         <v>57</v>
       </c>
       <c r="G39" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="H39" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2185,25 +2248,25 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D40" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E40" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F40" t="s">
         <v>57</v>
       </c>
       <c r="G40" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H40" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2211,25 +2274,25 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C41" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D41" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E41" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F41" t="s">
         <v>57</v>
       </c>
       <c r="G41" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H41" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2237,25 +2300,25 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D42" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E42" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F42" t="s">
         <v>57</v>
       </c>
       <c r="G42" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H42" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2263,25 +2326,25 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D43" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E43" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F43" t="s">
         <v>57</v>
       </c>
       <c r="G43" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H43" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2289,25 +2352,25 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D44" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E44" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F44" t="s">
         <v>57</v>
       </c>
       <c r="G44" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H44" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2315,25 +2378,25 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D45" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E45" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F45" t="s">
         <v>57</v>
       </c>
       <c r="G45" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H45" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2341,25 +2404,25 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D46" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E46" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F46" t="s">
         <v>57</v>
       </c>
       <c r="G46" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H46" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2367,25 +2430,25 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D47" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E47" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F47" t="s">
         <v>57</v>
       </c>
       <c r="G47" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H47" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2393,25 +2456,25 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D48" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E48" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F48" t="s">
         <v>57</v>
       </c>
       <c r="G48" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H48" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2419,25 +2482,25 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D49" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E49" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F49" t="s">
         <v>57</v>
       </c>
       <c r="G49" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H49" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2445,25 +2508,25 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D50" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E50" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F50" t="s">
         <v>57</v>
       </c>
       <c r="G50" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="H50" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2471,25 +2534,25 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D51" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E51" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F51" t="s">
         <v>57</v>
       </c>
       <c r="G51" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H51" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2497,25 +2560,25 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C52" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D52" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E52" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="F52" t="s">
         <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H52" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2523,25 +2586,25 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C53" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D53" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E53" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="F53" t="s">
         <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H53" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2549,25 +2612,25 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C54" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E54" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="F54" t="s">
         <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H54" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2575,25 +2638,25 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C55" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E55" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="F55" t="s">
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H55" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2601,25 +2664,25 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C56" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D56" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E56" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="F56" t="s">
         <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H56" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2627,25 +2690,25 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C57" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D57" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E57" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F57" t="s">
         <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="H57" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2653,25 +2716,25 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C58" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D58" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E58" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F58" t="s">
         <v>9</v>
       </c>
       <c r="G58" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="H58" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2679,25 +2742,25 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D59" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E59" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F59" t="s">
         <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="H59" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2705,25 +2768,25 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C60" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D60" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E60" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F60" t="s">
         <v>17</v>
       </c>
       <c r="G60" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="H60" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2731,25 +2794,25 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C61" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D61" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E61" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F61" t="s">
         <v>17</v>
       </c>
       <c r="G61" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="H61" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2757,25 +2820,25 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C62" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D62" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E62" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F62" t="s">
         <v>17</v>
       </c>
       <c r="G62" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="H62" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2783,25 +2846,25 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C63" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D63" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E63" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F63" t="s">
         <v>17</v>
       </c>
       <c r="G63" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H63" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2809,25 +2872,25 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C64" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D64" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E64" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F64" t="s">
         <v>17</v>
       </c>
       <c r="G64" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H64" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2835,25 +2898,25 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C65" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D65" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E65" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F65" t="s">
         <v>17</v>
       </c>
       <c r="G65" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H65" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2861,25 +2924,25 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C66" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D66" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E66" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F66" t="s">
         <v>17</v>
       </c>
       <c r="G66" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H66" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2887,25 +2950,25 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D67" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E67" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F67" t="s">
         <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H67" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2913,25 +2976,25 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C68" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D68" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E68" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F68" t="s">
         <v>17</v>
       </c>
       <c r="G68" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H68" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2939,25 +3002,25 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D69" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E69" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F69" t="s">
         <v>17</v>
       </c>
       <c r="G69" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H69" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2965,25 +3028,25 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C70" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D70" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E70" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F70" t="s">
         <v>17</v>
       </c>
       <c r="G70" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H70" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2991,25 +3054,25 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C71" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D71" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="E71" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="F71" t="s">
         <v>9</v>
       </c>
       <c r="G71" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="H71" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3017,25 +3080,25 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C72" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D72" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="E72" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="F72" t="s">
         <v>9</v>
       </c>
       <c r="G72" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="H72" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -3043,25 +3106,232 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C73" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D73" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="E73" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
       </c>
       <c r="G73" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="H73" t="s">
-        <v>201</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" t="s">
+        <v>160</v>
+      </c>
+      <c r="C74" t="s">
+        <v>177</v>
+      </c>
+      <c r="D74" t="s">
+        <v>180</v>
+      </c>
+      <c r="E74" t="s">
+        <v>177</v>
+      </c>
+      <c r="G74" t="s">
+        <v>189</v>
+      </c>
+      <c r="H74" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" t="s">
+        <v>177</v>
+      </c>
+      <c r="D75" t="s">
+        <v>180</v>
+      </c>
+      <c r="E75" t="s">
+        <v>177</v>
+      </c>
+      <c r="G75" t="s">
+        <v>189</v>
+      </c>
+      <c r="H75" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" t="s">
+        <v>177</v>
+      </c>
+      <c r="D76" t="s">
+        <v>180</v>
+      </c>
+      <c r="E76" t="s">
+        <v>177</v>
+      </c>
+      <c r="G76" t="s">
+        <v>189</v>
+      </c>
+      <c r="H76" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" t="s">
+        <v>163</v>
+      </c>
+      <c r="C77" t="s">
+        <v>177</v>
+      </c>
+      <c r="D77" t="s">
+        <v>180</v>
+      </c>
+      <c r="E77" t="s">
+        <v>177</v>
+      </c>
+      <c r="G77" t="s">
+        <v>189</v>
+      </c>
+      <c r="H77" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" t="s">
+        <v>177</v>
+      </c>
+      <c r="D78" t="s">
+        <v>180</v>
+      </c>
+      <c r="E78" t="s">
+        <v>177</v>
+      </c>
+      <c r="G78" t="s">
+        <v>189</v>
+      </c>
+      <c r="H78" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
+        <v>165</v>
+      </c>
+      <c r="C79" t="s">
+        <v>177</v>
+      </c>
+      <c r="D79" t="s">
+        <v>180</v>
+      </c>
+      <c r="E79" t="s">
+        <v>177</v>
+      </c>
+      <c r="G79" t="s">
+        <v>189</v>
+      </c>
+      <c r="H79" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C80" t="s">
+        <v>177</v>
+      </c>
+      <c r="D80" t="s">
+        <v>180</v>
+      </c>
+      <c r="E80" t="s">
+        <v>177</v>
+      </c>
+      <c r="G80" t="s">
+        <v>189</v>
+      </c>
+      <c r="H80" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" t="s">
+        <v>167</v>
+      </c>
+      <c r="C81" t="s">
+        <v>177</v>
+      </c>
+      <c r="D81" t="s">
+        <v>180</v>
+      </c>
+      <c r="E81" t="s">
+        <v>177</v>
+      </c>
+      <c r="G81" t="s">
+        <v>189</v>
+      </c>
+      <c r="H81" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" t="s">
+        <v>168</v>
+      </c>
+      <c r="C82" t="s">
+        <v>177</v>
+      </c>
+      <c r="D82" t="s">
+        <v>180</v>
+      </c>
+      <c r="E82" t="s">
+        <v>177</v>
+      </c>
+      <c r="G82" t="s">
+        <v>189</v>
+      </c>
+      <c r="H82" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3110,25 +3380,25 @@
         <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="H2" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3136,25 +3406,25 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="H3" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3162,25 +3432,25 @@
         <v>79</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="H4" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3200,289 +3470,289 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B1" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="C1" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="D1" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="E1" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="F1" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="G1" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="D2" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G2" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G3" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="D4" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G4" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="D5" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="E5" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="F5" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="G5" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C6" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="D6" t="s">
         <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="F6" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G6" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="D7" t="s">
         <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="F7" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="G7" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="D8" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G8" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C9" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="F9" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G9" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B10" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C10" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D10" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="E10" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="F10" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G10" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="B11" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D11" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G11" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C12" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D12" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G12" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="B13" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C13" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -3491,21 +3761,21 @@
         <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G13" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="B14" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -3514,21 +3784,21 @@
         <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G14" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="B15" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C15" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
@@ -3537,21 +3807,21 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G15" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D16" t="s">
         <v>41</v>
@@ -3560,21 +3830,21 @@
         <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G16" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C17" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D17" t="s">
         <v>43</v>
@@ -3583,21 +3853,21 @@
         <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G17" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D18" t="s">
         <v>42</v>
@@ -3606,21 +3876,21 @@
         <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G18" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D19" t="s">
         <v>56</v>
@@ -3629,21 +3899,21 @@
         <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G19" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C20" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D20" t="s">
         <v>45</v>
@@ -3652,44 +3922,44 @@
         <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G20" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C21" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="F21" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G21" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C22" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D22" t="s">
         <v>66</v>
@@ -3698,125 +3968,125 @@
         <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G22" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C23" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D23" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G23" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C24" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D24" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E24" t="s">
         <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G24" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D25" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E25" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="F25" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G25" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C26" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D26" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E26" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="F26" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G26" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D27" t="s">
         <v>76</v>
       </c>
       <c r="E27" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="F27" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G27" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -3865,25 +4135,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H2" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3891,25 +4161,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H3" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3917,25 +4187,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H4" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3943,25 +4213,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H5" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3969,25 +4239,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H6" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3995,25 +4265,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E7" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H7" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4021,25 +4291,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E8" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H8" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4047,25 +4317,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E9" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H9" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4073,25 +4343,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E10" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H10" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -4140,25 +4410,25 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H2" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4166,25 +4436,25 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="H3" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4192,25 +4462,25 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E4" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="H4" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4218,25 +4488,25 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E5" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4244,25 +4514,25 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E6" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H6" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4270,25 +4540,25 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E7" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="H7" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4296,25 +4566,25 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E8" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="H8" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4322,25 +4592,25 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E9" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="H9" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4348,25 +4618,25 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E10" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="H10" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4374,25 +4644,25 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E11" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="H11" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4400,25 +4670,25 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E12" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="H12" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4426,25 +4696,25 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E13" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H13" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4452,25 +4722,25 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E14" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H14" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4478,25 +4748,25 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E15" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H15" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4504,25 +4774,25 @@
         <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E16" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H16" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4530,25 +4800,25 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D17" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E17" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F17" t="s">
         <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H17" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4556,25 +4826,25 @@
         <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H18" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -4623,25 +4893,25 @@
         <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H2" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4649,25 +4919,25 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H3" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4675,25 +4945,25 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F4" t="s">
         <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H4" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4701,25 +4971,25 @@
         <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F5" t="s">
         <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4727,25 +4997,25 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E6" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F6" t="s">
         <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H6" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4753,25 +5023,25 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F7" t="s">
         <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H7" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4779,25 +5049,25 @@
         <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E8" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F8" t="s">
         <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H8" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4805,25 +5075,25 @@
         <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E9" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F9" t="s">
         <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="H9" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4831,25 +5101,25 @@
         <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F10" t="s">
         <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="H10" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4857,25 +5127,25 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F11" t="s">
         <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="H11" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4883,25 +5153,25 @@
         <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F12" t="s">
         <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="H12" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4909,25 +5179,25 @@
         <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F13" t="s">
         <v>57</v>
       </c>
       <c r="G13" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="H13" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4935,25 +5205,25 @@
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E14" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F14" t="s">
         <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H14" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4961,25 +5231,25 @@
         <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C15" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E15" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F15" t="s">
         <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H15" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4987,25 +5257,25 @@
         <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E16" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F16" t="s">
         <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H16" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -5013,25 +5283,25 @@
         <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E17" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F17" t="s">
         <v>57</v>
       </c>
       <c r="G17" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H17" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -5039,25 +5309,25 @@
         <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E18" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H18" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -5065,25 +5335,25 @@
         <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E19" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F19" t="s">
         <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H19" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -5091,25 +5361,25 @@
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E20" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F20" t="s">
         <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H20" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -5117,25 +5387,25 @@
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E21" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H21" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -5143,25 +5413,25 @@
         <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E22" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F22" t="s">
         <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H22" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -5169,25 +5439,25 @@
         <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E23" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F23" t="s">
         <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H23" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -5195,25 +5465,25 @@
         <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E24" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F24" t="s">
         <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="H24" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5221,25 +5491,25 @@
         <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D25" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E25" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F25" t="s">
         <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="H25" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -5288,25 +5558,25 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C2" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H2" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5314,25 +5584,25 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H3" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -5381,25 +5651,25 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H2" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5407,25 +5677,25 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H3" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -5433,25 +5703,25 @@
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H4" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -5500,25 +5770,25 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="H2" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5526,25 +5796,25 @@
         <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="H3" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -5552,25 +5822,25 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="H4" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -5619,25 +5889,25 @@
         <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="H2" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5645,25 +5915,25 @@
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="H3" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -5671,25 +5941,25 @@
         <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="H4" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -5697,25 +5967,25 @@
         <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -5723,25 +5993,25 @@
         <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H6" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -5749,25 +6019,25 @@
         <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H7" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -5775,25 +6045,25 @@
         <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H8" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -5801,25 +6071,25 @@
         <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E9" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H9" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -5827,25 +6097,25 @@
         <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E10" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H10" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -5853,25 +6123,25 @@
         <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E11" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H11" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -5879,25 +6149,25 @@
         <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E12" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H12" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/banco_de_dados/entrega_orientadora/Dicionario_Variaveis_Projeto.xlsx
+++ b/banco_de_dados/entrega_orientadora/Dicionario_Variaveis_Projeto.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="294">
   <si>
     <t>variavel</t>
   </si>
@@ -160,6 +160,9 @@
     <t>V00236</t>
   </si>
   <si>
+    <t>V00237</t>
+  </si>
+  <si>
     <t>V00238</t>
   </si>
   <si>
@@ -403,6 +406,9 @@
     <t>Domicílios Particulares Permanentes Ocupados, Apenas banheiro de uso comum a mais de um domicílio</t>
   </si>
   <si>
+    <t>Domicílios Particulares Permanentes Ocupados, Apenas sanitário ou buraco para dejeções, inclusive os localizados no terreno</t>
+  </si>
+  <si>
     <t>Domicílios Particulares Permanentes Ocupados, Não tinham banheiro nem sanitário</t>
   </si>
   <si>
@@ -598,7 +604,7 @@
     <t>pct_raca_pretpardind, pct_crianca_0a4, pct_pop_0a14, pct_idoso_60mais</t>
   </si>
   <si>
-    <t>pct_agua_inad, pct_esgoto_inad, pct_lixo_inad, razao_moradores, pct_dom_improv, pct_hab_precaria, pct_moradia_convencional, pct_moradia_nao_convencional, pct_apartamento, pct_casa, pct_casa_vila_condominio, pct_sem_agua_canalizada, pct_agua_nao_encanada, pct_agua_so_terreno, pct_sem_banheiro, pct_sem_banheiro_nem_sanitario</t>
+    <t>pct_agua_inad, pct_esgoto_inad, pct_lixo_inad, razao_moradores, pct_dom_improv, pct_hab_precaria, pct_moradia_convencional, pct_moradia_nao_convencional, pct_apartamento, pct_casa, pct_casa_vila_condominio, pct_sem_agua_canalizada, pct_agua_nao_encanada, pct_agua_so_terreno, pct_sem_banheiro, pct_sem_banheiro_nem_sanitario, pct_so_sanitario, pct_banheiro_comum</t>
   </si>
   <si>
     <t>razao_moradores, pct_dom_improv, pct_hab_precaria</t>
@@ -637,7 +643,10 @@
     <t>pct_agua_nao_encanada</t>
   </si>
   <si>
-    <t>(conferência) banheiro de uso comum; completa o bloco de banheiro junto de V00238 e V00495</t>
+    <t>pct_banheiro_comum</t>
+  </si>
+  <si>
+    <t>pct_so_sanitario</t>
   </si>
   <si>
     <t>pct_sem_banheiro_nem_sanitario</t>
@@ -869,6 +878,12 @@
   </si>
   <si>
     <t>Proporção de domicílios sem banheiro nem sanitário</t>
+  </si>
+  <si>
+    <t>Proporção de domicílios com apenas sanitário ou buraco para dejeções</t>
+  </si>
+  <si>
+    <t>Proporção de domicílios com apenas banheiro de uso comum</t>
   </si>
   <si>
     <t>Proporção de domicílios com pessoa responsável do sexo feminino</t>
@@ -1221,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1260,25 +1275,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1286,25 +1301,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1312,25 +1327,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1338,25 +1353,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1364,25 +1379,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1390,25 +1405,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1416,25 +1431,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1442,25 +1457,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1468,25 +1483,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1494,25 +1509,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H11" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1520,25 +1535,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1546,25 +1561,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1572,25 +1587,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1598,25 +1613,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1624,25 +1639,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D16" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E16" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1650,25 +1665,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E17" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F17" t="s">
         <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H17" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1676,25 +1691,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H18" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1702,25 +1717,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E19" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F19" t="s">
         <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H19" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1728,25 +1743,25 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H20" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1754,25 +1769,25 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D21" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E21" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H21" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1780,25 +1795,25 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E22" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F22" t="s">
         <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H22" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1806,25 +1821,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D23" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F23" t="s">
         <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H23" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1832,25 +1847,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D24" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E24" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H24" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1858,25 +1873,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D25" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E25" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F25" t="s">
         <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H25" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1884,25 +1899,25 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E26" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F26" t="s">
         <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H26" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1910,25 +1925,25 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D27" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E27" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F27" t="s">
         <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H27" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1936,25 +1951,25 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H28" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1962,25 +1977,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D29" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E29" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G29" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H29" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1988,25 +2003,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D30" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G30" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H30" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2014,25 +2029,25 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E31" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G31" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H31" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2040,25 +2055,25 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D32" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E32" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G32" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H32" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2066,25 +2081,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G33" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H33" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2092,25 +2107,25 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D34" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G34" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H34" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2118,25 +2133,25 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D35" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E35" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G35" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H35" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2144,25 +2159,25 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D36" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E36" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G36" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H36" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2170,25 +2185,25 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D37" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G37" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H37" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2196,25 +2211,25 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G38" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H38" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2222,25 +2237,25 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D39" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E39" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G39" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H39" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2248,25 +2263,25 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D40" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E40" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G40" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H40" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2274,25 +2289,25 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E41" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G41" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H41" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2300,25 +2315,25 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D42" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G42" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H42" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2326,25 +2341,25 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D43" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E43" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G43" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2352,25 +2367,25 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D44" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E44" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G44" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H44" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2378,25 +2393,25 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D45" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E45" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G45" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H45" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2404,25 +2419,25 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D46" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E46" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F46" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G46" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H46" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2430,25 +2445,25 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D47" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E47" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F47" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G47" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H47" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2456,25 +2471,25 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D48" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E48" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G48" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H48" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2482,25 +2497,25 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D49" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E49" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G49" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H49" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2508,25 +2523,25 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H50" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2534,25 +2549,25 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="C51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D51" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E51" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G51" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="H51" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2560,25 +2575,25 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D52" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E52" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F52" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G52" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="H52" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2586,25 +2601,25 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E53" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F53" t="s">
         <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H53" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2612,25 +2627,25 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F54" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H54" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2638,25 +2653,25 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D55" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E55" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F55" t="s">
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H55" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2664,25 +2679,25 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C56" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D56" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E56" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F56" t="s">
         <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H56" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2690,25 +2705,25 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F57" t="s">
         <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H57" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2716,25 +2731,25 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C58" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D58" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E58" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F58" t="s">
         <v>9</v>
       </c>
       <c r="G58" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H58" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2742,25 +2757,25 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C59" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D59" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E59" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F59" t="s">
         <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H59" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2768,25 +2783,25 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E60" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F60" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G60" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H60" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2794,25 +2809,25 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C61" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D61" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E61" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F61" t="s">
         <v>17</v>
       </c>
       <c r="G61" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H61" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2820,25 +2835,25 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C62" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D62" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E62" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F62" t="s">
         <v>17</v>
       </c>
       <c r="G62" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H62" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2846,25 +2861,25 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C63" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D63" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E63" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F63" t="s">
         <v>17</v>
       </c>
       <c r="G63" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H63" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2872,25 +2887,25 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F64" t="s">
         <v>17</v>
       </c>
       <c r="G64" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H64" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2898,25 +2913,25 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C65" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D65" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E65" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F65" t="s">
         <v>17</v>
       </c>
       <c r="G65" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H65" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2924,25 +2939,25 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D66" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E66" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F66" t="s">
         <v>17</v>
       </c>
       <c r="G66" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H66" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2950,25 +2965,25 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C67" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D67" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E67" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F67" t="s">
         <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H67" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2976,25 +2991,25 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C68" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D68" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E68" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F68" t="s">
         <v>17</v>
       </c>
       <c r="G68" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H68" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -3002,25 +3017,25 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C69" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D69" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E69" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F69" t="s">
         <v>17</v>
       </c>
       <c r="G69" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H69" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -3028,25 +3043,25 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C70" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D70" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E70" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F70" t="s">
         <v>17</v>
       </c>
       <c r="G70" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H70" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -3054,25 +3069,25 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D71" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E71" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F71" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G71" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H71" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3080,25 +3095,25 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C72" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D72" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E72" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F72" t="s">
         <v>9</v>
       </c>
       <c r="G72" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H72" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -3106,25 +3121,25 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C73" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D73" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E73" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
       </c>
       <c r="G73" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H73" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3132,22 +3147,25 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C74" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D74" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E74" t="s">
-        <v>177</v>
+        <v>190</v>
+      </c>
+      <c r="F74" t="s">
+        <v>9</v>
       </c>
       <c r="G74" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="H74" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -3155,22 +3173,22 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C75" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D75" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E75" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G75" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H75" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -3178,22 +3196,22 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C76" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D76" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E76" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G76" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H76" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -3201,22 +3219,22 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C77" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D77" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E77" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G77" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H77" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -3224,22 +3242,22 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C78" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D78" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E78" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G78" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H78" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3247,22 +3265,22 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D79" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E79" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G79" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H79" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -3270,22 +3288,22 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C80" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D80" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E80" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G80" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H80" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -3293,22 +3311,22 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C81" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D81" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E81" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G81" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H81" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -3316,22 +3334,45 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D82" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E82" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G82" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H82" t="s">
-        <v>222</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" t="s">
+        <v>179</v>
+      </c>
+      <c r="D83" t="s">
+        <v>182</v>
+      </c>
+      <c r="E83" t="s">
+        <v>179</v>
+      </c>
+      <c r="G83" t="s">
+        <v>191</v>
+      </c>
+      <c r="H83" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3377,80 +3418,80 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -3460,7 +3501,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -3470,289 +3511,289 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G6" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D8" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F9" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C10" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D10" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E10" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F10" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B11" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B13" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -3761,21 +3802,21 @@
         <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C14" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -3784,21 +3825,21 @@
         <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B15" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C15" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
@@ -3807,21 +3848,21 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G15" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D16" t="s">
         <v>41</v>
@@ -3830,21 +3871,21 @@
         <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G16" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D17" t="s">
         <v>43</v>
@@ -3853,21 +3894,21 @@
         <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G17" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D18" t="s">
         <v>42</v>
@@ -3876,217 +3917,263 @@
         <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C19" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
         <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G19" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G20" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>258</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G21" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="C22" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="C23" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D23" t="s">
-        <v>253</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>261</v>
       </c>
       <c r="F23" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G23" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C24" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D24" t="s">
-        <v>254</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s">
         <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G24" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C25" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D25" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E25" t="s">
-        <v>253</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G25" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C26" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D26" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E26" t="s">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G26" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C27" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>257</v>
       </c>
       <c r="E27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F27" t="s">
+        <v>265</v>
+      </c>
+      <c r="G27" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>219</v>
+      </c>
+      <c r="B28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" t="s">
+        <v>247</v>
+      </c>
+      <c r="D28" t="s">
+        <v>257</v>
+      </c>
+      <c r="E28" t="s">
         <v>262</v>
       </c>
-      <c r="G27" t="s">
-        <v>288</v>
+      <c r="F28" t="s">
+        <v>265</v>
+      </c>
+      <c r="G28" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>242</v>
+      </c>
+      <c r="B29" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" t="s">
+        <v>247</v>
+      </c>
+      <c r="D29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" t="s">
+        <v>257</v>
+      </c>
+      <c r="F29" t="s">
+        <v>265</v>
+      </c>
+      <c r="G29" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -4135,25 +4222,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4161,25 +4248,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4187,25 +4274,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4213,25 +4300,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4239,25 +4326,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4265,25 +4352,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4291,25 +4378,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4317,25 +4404,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4343,25 +4430,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -4410,25 +4497,25 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4436,25 +4523,25 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4462,25 +4549,25 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4488,25 +4575,25 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4514,25 +4601,25 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4540,25 +4627,25 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4566,25 +4653,25 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4592,25 +4679,25 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4618,25 +4705,25 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4644,25 +4731,25 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H11" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4670,25 +4757,25 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4696,25 +4783,25 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4722,25 +4809,25 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4748,25 +4835,25 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4774,25 +4861,25 @@
         <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D16" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E16" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4800,25 +4887,25 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E17" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F17" t="s">
         <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H17" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4826,25 +4913,25 @@
         <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H18" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -4854,7 +4941,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4893,25 +4980,25 @@
         <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4919,25 +5006,25 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4945,25 +5032,25 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4971,25 +5058,25 @@
         <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4997,25 +5084,25 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -5023,25 +5110,25 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -5049,25 +5136,25 @@
         <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -5075,25 +5162,25 @@
         <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -5101,25 +5188,25 @@
         <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -5127,25 +5214,25 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H11" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -5153,25 +5240,25 @@
         <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -5179,25 +5266,25 @@
         <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G13" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -5205,25 +5292,25 @@
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -5231,25 +5318,25 @@
         <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -5257,25 +5344,25 @@
         <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D16" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E16" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G16" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -5283,25 +5370,25 @@
         <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H17" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -5309,25 +5396,25 @@
         <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D18" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E18" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G18" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H18" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -5335,25 +5422,25 @@
         <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H19" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -5361,25 +5448,25 @@
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H20" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -5387,25 +5474,25 @@
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D21" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G21" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H21" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -5413,25 +5500,25 @@
         <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D22" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E22" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G22" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H22" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -5439,25 +5526,25 @@
         <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G23" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H23" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -5465,25 +5552,25 @@
         <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D24" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E24" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G24" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H24" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5491,25 +5578,51 @@
         <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="C25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D25" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G25" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="H25" t="s">
-        <v>220</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" t="s">
+        <v>191</v>
+      </c>
+      <c r="H26" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -5555,54 +5668,54 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5648,80 +5761,80 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5767,80 +5880,80 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5886,288 +5999,288 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H11" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
